--- a/artfynd/A 65905-2021 artfynd.xlsx
+++ b/artfynd/A 65905-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65905-2021 artfynd.xlsx
+++ b/artfynd/A 65905-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89603306</v>
+        <v>89603279</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425903.1809954656</v>
+        <v>425837</v>
       </c>
       <c r="R2" t="n">
-        <v>6937442.932773868</v>
+        <v>6937477</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89603280</v>
+        <v>89603289</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>426132.216332101</v>
+        <v>426152</v>
       </c>
       <c r="R3" t="n">
-        <v>6937500.105620679</v>
+        <v>6937413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89603249</v>
+        <v>89603269</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425937.8002579631</v>
+        <v>425908</v>
       </c>
       <c r="R4" t="n">
-        <v>6937400.178287406</v>
+        <v>6937436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89603259</v>
+        <v>89603305</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425966.7742036738</v>
+        <v>426039</v>
       </c>
       <c r="R5" t="n">
-        <v>6937497.795533854</v>
+        <v>6937430</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89603269</v>
+        <v>89603260</v>
       </c>
       <c r="B6" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425908.1059578058</v>
+        <v>426068</v>
       </c>
       <c r="R6" t="n">
-        <v>6937435.902790814</v>
+        <v>6937413</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89603281</v>
+        <v>89603264</v>
       </c>
       <c r="B7" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426148.8805267517</v>
+        <v>426149</v>
       </c>
       <c r="R7" t="n">
-        <v>6937480.820350596</v>
+        <v>6937417</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1248,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89603256</v>
+        <v>89603280</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426139.9732152169</v>
+        <v>426132</v>
       </c>
       <c r="R8" t="n">
-        <v>6937371.221044033</v>
+        <v>6937500</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1349,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89603271</v>
+        <v>89603281</v>
       </c>
       <c r="B9" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426115.2135177021</v>
+        <v>426149</v>
       </c>
       <c r="R9" t="n">
-        <v>6937504.174766256</v>
+        <v>6937481</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,19 +1450,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89603303</v>
+        <v>89603240</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>426141.7794132519</v>
+        <v>426152</v>
       </c>
       <c r="R10" t="n">
-        <v>6937410.856008608</v>
+        <v>6937413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,19 +1551,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89603242</v>
+        <v>89603266</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425927.2278903091</v>
+        <v>426033</v>
       </c>
       <c r="R11" t="n">
-        <v>6937506.059310211</v>
+        <v>6937540</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,19 +1652,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89603292</v>
+        <v>89603249</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426121.9022598615</v>
+        <v>425938</v>
       </c>
       <c r="R12" t="n">
-        <v>6937348.094796621</v>
+        <v>6937400</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,19 +1753,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89603289</v>
+        <v>89603251</v>
       </c>
       <c r="B13" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>426151.9896163532</v>
+        <v>425946</v>
       </c>
       <c r="R13" t="n">
-        <v>6937412.935446611</v>
+        <v>6937520</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,19 +1854,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,15 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89603278</v>
+        <v>89603256</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,21 +1898,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2107,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426137.7978819394</v>
+        <v>426140</v>
       </c>
       <c r="R14" t="n">
-        <v>6937398.027187187</v>
+        <v>6937371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,19 +1955,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89603301</v>
+        <v>89603259</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426071.1732473667</v>
+        <v>425967</v>
       </c>
       <c r="R15" t="n">
-        <v>6937538.832164845</v>
+        <v>6937498</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,19 +2056,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,15 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89603290</v>
+        <v>89603271</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426133.9299155003</v>
+        <v>426115</v>
       </c>
       <c r="R16" t="n">
-        <v>6937494.070255177</v>
+        <v>6937504</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,19 +2157,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,15 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89603310</v>
+        <v>89603273</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2455,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425868.849265242</v>
+        <v>425887</v>
       </c>
       <c r="R17" t="n">
-        <v>6937477.838109309</v>
+        <v>6937493</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,19 +2258,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,15 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89603308</v>
+        <v>89603287</v>
       </c>
       <c r="B18" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2571,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>426061.8361057298</v>
+        <v>426142</v>
       </c>
       <c r="R18" t="n">
-        <v>6937555.18634633</v>
+        <v>6937411</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2604,19 +2359,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2647,15 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89603305</v>
+        <v>89603306</v>
       </c>
       <c r="B19" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2687,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426039.1854759858</v>
+        <v>425903</v>
       </c>
       <c r="R19" t="n">
-        <v>6937430.210549631</v>
+        <v>6937443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,19 +2460,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,37 +2493,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89603264</v>
+        <v>89603250</v>
       </c>
       <c r="B20" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2803,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426148.8496046772</v>
+        <v>426004</v>
       </c>
       <c r="R20" t="n">
-        <v>6937417.157350787</v>
+        <v>6937421</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,19 +2561,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2879,37 +2594,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89603273</v>
+        <v>89603263</v>
       </c>
       <c r="B21" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2919,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425887.2080178741</v>
+        <v>426054</v>
       </c>
       <c r="R21" t="n">
-        <v>6937493.113158715</v>
+        <v>6937419</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2952,19 +2662,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,37 +2695,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89603266</v>
+        <v>89603270</v>
       </c>
       <c r="B22" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3035,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426032.8582694014</v>
+        <v>425902</v>
       </c>
       <c r="R22" t="n">
-        <v>6937540.147377342</v>
+        <v>6937460</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3068,19 +2763,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3111,37 +2796,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89603299</v>
+        <v>89603288</v>
       </c>
       <c r="B23" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3151,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426043.9367292639</v>
+        <v>426070</v>
       </c>
       <c r="R23" t="n">
-        <v>6937436.101994067</v>
+        <v>6937328</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,19 +2864,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3227,37 +2897,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89603260</v>
+        <v>89603292</v>
       </c>
       <c r="B24" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3267,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426067.9068405181</v>
+        <v>426122</v>
       </c>
       <c r="R24" t="n">
-        <v>6937412.962423892</v>
+        <v>6937348</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3300,19 +2965,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3343,37 +2998,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89603285</v>
+        <v>89603301</v>
       </c>
       <c r="B25" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3383,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426033.2236414128</v>
+        <v>426071</v>
       </c>
       <c r="R25" t="n">
-        <v>6937432.188776162</v>
+        <v>6937539</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3416,19 +3066,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3459,37 +3099,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89603287</v>
+        <v>89603310</v>
       </c>
       <c r="B26" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3499,10 +3134,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426141.7794132519</v>
+        <v>425869</v>
       </c>
       <c r="R26" t="n">
-        <v>6937410.856008608</v>
+        <v>6937478</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3532,19 +3167,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3575,15 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89603240</v>
+        <v>89603295</v>
       </c>
       <c r="B27" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,21 +3211,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3615,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426152.0101402009</v>
+        <v>426093</v>
       </c>
       <c r="R27" t="n">
-        <v>6937413.857661814</v>
+        <v>6937521</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,19 +3268,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3684,818 +3294,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>89603276</v>
-      </c>
-      <c r="B28" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Stornäshållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>425956.8768561377</v>
-      </c>
-      <c r="R28" t="n">
-        <v>6937406.211307552</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>89603274</v>
-      </c>
-      <c r="B29" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Stornäshållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>426110.1838368753</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6937382.033745003</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>89603250</v>
-      </c>
-      <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Stornäshållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>426003.8651037264</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6937420.848620155</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>89603270</v>
-      </c>
-      <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Stornäshållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>425902.1766825268</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6937460.024501474</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>89603288</v>
-      </c>
-      <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Stornäshållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>426070.1724938734</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6937328.024925884</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>89603251</v>
-      </c>
-      <c r="B33" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Stornäshållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>425946.0170935945</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6937519.94095681</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>89603263</v>
-      </c>
-      <c r="B34" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Stornäshållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>426054.1771180776</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6937418.804389974</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 65905-2021 artfynd.xlsx
+++ b/artfynd/A 65905-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603279</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603305</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603260</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603264</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603280</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603281</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603240</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603266</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603249</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603251</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603256</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603259</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603271</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603273</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603287</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603306</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603250</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603263</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603270</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603288</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603292</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603301</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603310</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,8 +3428,41 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603295</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>